--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484058_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484058_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3884</v>
+        <v>4.6255</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3291</v>
+        <v>4.1453</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0593</v>
+        <v>0.4802</v>
       </c>
       <c r="G2" t="n">
         <v>5.7989</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9381</v>
+        <v>0.299</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0485</v>
+        <v>-0.2323</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1105</v>
+        <v>0.5313</v>
       </c>
       <c r="V2" t="n">
         <v>-1.4724</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9146</v>
+        <v>2.402</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2369</v>
+        <v>0.0328</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6778</v>
+        <v>2.3692</v>
       </c>
       <c r="G3" t="n">
         <v>0.3788</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1189</v>
+        <v>-0.323</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="V3" t="n">
         <v>2.4129</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TROUVE CASELLAS</t>
+          <t>O. NGOMO MIFUMU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9124</v>
+        <v>1.9805</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3148</v>
+        <v>1.2579</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5975</v>
+        <v>0.7226</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0568</v>
+        <v>1.3406</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4156</v>
+        <v>1.1087</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6412</v>
+        <v>0.2319</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4881</v>
+        <v>1.3032</v>
       </c>
       <c r="K4" t="n">
-        <v>1.996</v>
+        <v>1.2203</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4921</v>
+        <v>0.0829</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4314</v>
+        <v>0.0374</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5804</v>
+        <v>-0.1116</v>
       </c>
       <c r="O4" t="n">
         <v>0.149</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.9596</v>
+        <v>0.9919</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.9515</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1958</v>
+        <v>0.5172</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2301</v>
+        <v>-0.0453</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9657</v>
+        <v>0.5625</v>
       </c>
       <c r="V4" t="n">
-        <v>3.6194</v>
+        <v>-0.8692</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5481</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0713</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. IGLESIAS GARCIA</t>
+          <t>A. TROUVE CASELLAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2664</v>
+        <v>1.5554</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0509</v>
+        <v>0.2945</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3173</v>
+        <v>1.2609</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6764</v>
+        <v>2.0568</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2541</v>
+        <v>1.4156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4223</v>
+        <v>0.6412</v>
       </c>
       <c r="J5" t="n">
-        <v>1.621</v>
+        <v>2.4881</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0887</v>
+        <v>1.996</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5323</v>
+        <v>0.4921</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0553</v>
+        <v>-0.4314</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1653</v>
+        <v>-0.5804</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.11</v>
+        <v>0.149</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1984</v>
+        <v>-4.9596</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>-5.9515</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7884</v>
+        <v>0.8389</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3119</v>
+        <v>0.2098</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4766</v>
+        <v>0.6291</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3.6194</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.5481</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. NGOMO MIFUMU</t>
+          <t>A. IGLESIAS GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1667</v>
+        <v>1.468</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3599</v>
+        <v>-0.7651</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8068</v>
+        <v>2.2332</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3406</v>
+        <v>1.6764</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1087</v>
+        <v>1.2541</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2319</v>
+        <v>0.4223</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3032</v>
+        <v>1.621</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2203</v>
+        <v>1.0887</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0829</v>
+        <v>0.5323</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0374</v>
+        <v>0.0553</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1116</v>
+        <v>0.1653</v>
       </c>
       <c r="O6" t="n">
-        <v>0.149</v>
+        <v>-0.11</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q6" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.7855</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.4023</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="V6" t="n">
         <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.9919</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.7034</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.0567</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.6466</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.8692</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9826</v>
+        <v>1.457</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9962</v>
+        <v>-0.6901</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9787</v>
+        <v>2.1471</v>
       </c>
       <c r="G7" t="n">
         <v>-0.286</v>
@@ -1000,13 +1000,13 @@
         <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1995</v>
+        <v>0.2749</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3514</v>
+        <v>-0.0453</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1519</v>
+        <v>0.3202</v>
       </c>
       <c r="V7" t="n">
         <v>0.6745</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7083</v>
+        <v>0.6802</v>
       </c>
       <c r="E8" t="n">
         <v>-0.3043</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0125</v>
+        <v>0.9845</v>
       </c>
       <c r="G8" t="n">
         <v>1.4124</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2398</v>
+        <v>-0.2678</v>
       </c>
       <c r="T8" t="n">
         <v>-0.3004</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0606</v>
+        <v>0.0325</v>
       </c>
       <c r="V8" t="n">
         <v>-0.266</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1409</v>
+        <v>-0.2353</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2056</v>
+        <v>-2.1036</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0647</v>
+        <v>1.8683</v>
       </c>
       <c r="G9" t="n">
         <v>0.8179999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0844</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3514</v>
+        <v>-0.2493</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4358</v>
+        <v>0.2394</v>
       </c>
       <c r="V9" t="n">
         <v>0.9405</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8233</v>
+        <v>-0.9867</v>
       </c>
       <c r="E10" t="n">
-        <v>0.226</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0494</v>
+        <v>-1.8249</v>
       </c>
       <c r="G10" t="n">
         <v>1.3056</v>
@@ -1234,13 +1234,13 @@
         <v>1.9838</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1767</v>
+        <v>-0.3401</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9238</v>
+        <v>-0.3117</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2529</v>
+        <v>-0.0284</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9522</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1528</v>
+        <v>-3.7243</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8468</v>
+        <v>-4.6428</v>
       </c>
       <c r="F11" t="n">
-        <v>0.694</v>
+        <v>0.9184</v>
       </c>
       <c r="G11" t="n">
         <v>0.3166</v>
@@ -1312,13 +1312,13 @@
         <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2358</v>
+        <v>0.1927</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4307</v>
+        <v>-0.2266</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1949</v>
+        <v>0.4193</v>
       </c>
       <c r="V11" t="n">
         <v>-0.266</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.2224</v>
+        <v>9.222299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9371</v>
+        <v>-1.937200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>11.1592</v>
+        <v>11.1595</v>
       </c>
       <c r="G12" t="n">
         <v>14.8181</v>
@@ -1366,7 +1366,7 @@
         <v>14.0914</v>
       </c>
       <c r="K12" t="n">
-        <v>8.975099999999999</v>
+        <v>8.975100000000001</v>
       </c>
       <c r="L12" t="n">
         <v>5.116400000000001</v>
@@ -1390,7 +1390,7 @@
         <v>13.8867</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5018</v>
+        <v>1.502</v>
       </c>
       <c r="T12" t="n">
         <v>-1.9264</v>
@@ -1405,7 +1405,7 @@
         <v>9.703799999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.882400000000001</v>
+        <v>-6.8824</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1735</v>
+        <v>4.2451</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0911</v>
+        <v>3.2749</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0824</v>
+        <v>0.9702</v>
       </c>
       <c r="G13" t="n">
         <v>2.7134</v>
@@ -1468,13 +1468,13 @@
         <v>3.1741</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6313</v>
+        <v>0.7029</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0034</v>
+        <v>0.1872</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6279</v>
+        <v>0.5157</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1469</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8016</v>
+        <v>3.8867</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9052</v>
+        <v>2.191</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8964</v>
+        <v>1.6957</v>
       </c>
       <c r="G14" t="n">
         <v>0.4952</v>
@@ -1546,13 +1546,13 @@
         <v>3.5709</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5724</v>
+        <v>0.6575</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0148</v>
+        <v>0.3006</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5576</v>
+        <v>0.357</v>
       </c>
       <c r="V14" t="n">
         <v>1.5437</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6037</v>
+        <v>0.71</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5193</v>
+        <v>0.2132</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0844</v>
+        <v>0.4968</v>
       </c>
       <c r="G15" t="n">
         <v>-1.4198</v>
@@ -1624,13 +1624,13 @@
         <v>2.9758</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4166</v>
+        <v>-0.3103</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.493</v>
+        <v>-0.7991</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0764</v>
+        <v>0.4888</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3373</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4871</v>
+        <v>0.3835</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2976</v>
+        <v>0.2126</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1895</v>
+        <v>0.171</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4643</v>
@@ -1702,13 +1702,13 @@
         <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6099</v>
+        <v>0.2608</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4874</v>
+        <v>0.0227</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1224</v>
+        <v>0.238</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6032</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2362</v>
+        <v>-1.1486</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2186</v>
+        <v>-2.0146</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.8659</v>
       </c>
       <c r="G17" t="n">
         <v>-1.9092</v>
@@ -1780,13 +1780,13 @@
         <v>2.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5255</v>
+        <v>-0.4379</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0995</v>
+        <v>-0.8955</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.4576</v>
       </c>
       <c r="V17" t="n">
         <v>0.6032</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1563</v>
+        <v>-2.5025</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.6409</v>
+        <v>-3.9267</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4846</v>
+        <v>1.4243</v>
       </c>
       <c r="G18" t="n">
         <v>-4.2695</v>
@@ -1858,13 +1858,13 @@
         <v>3.1741</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.216</v>
+        <v>0.4379</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0995</v>
+        <v>-0.3853</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8835</v>
+        <v>0.8232</v>
       </c>
       <c r="V18" t="n">
         <v>0.3373</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5177</v>
+        <v>-3.0314</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2684</v>
+        <v>-1.1664</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2493</v>
+        <v>-1.865</v>
       </c>
       <c r="G19" t="n">
         <v>-3.5363</v>
@@ -1936,13 +1936,13 @@
         <v>1.7855</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3025</v>
+        <v>-0.8162</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0485</v>
+        <v>-0.9465</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.254</v>
+        <v>0.1303</v>
       </c>
       <c r="V19" t="n">
         <v>-0.266</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.6659</v>
+        <v>-4.2672</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.1967</v>
+        <v>-4.2988</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4692</v>
+        <v>0.0316</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7788</v>
@@ -2014,13 +2014,13 @@
         <v>3.3725</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8791</v>
+        <v>-0.4803</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4817</v>
+        <v>-0.5837</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3974</v>
+        <v>0.1034</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2065</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.7378</v>
+        <v>-6.1375</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.3187</v>
+        <v>-5.9105</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4191</v>
+        <v>-0.227</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6488</v>
@@ -2092,13 +2092,13 @@
         <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7561</v>
+        <v>-0.1559</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7368</v>
+        <v>-0.3287</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0193</v>
+        <v>0.1728</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7458</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.222200000000001</v>
+        <v>-7.861899999999999</v>
       </c>
       <c r="E22" t="n">
         <v>-11.4253</v>
       </c>
       <c r="F22" t="n">
-        <v>2.203100000000001</v>
+        <v>3.5635</v>
       </c>
       <c r="G22" t="n">
         <v>-14.8181</v>
@@ -2170,13 +2170,13 @@
         <v>23.8061</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.502</v>
+        <v>-0.1415000000000003</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.428199999999999</v>
+        <v>-3.4283</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9264</v>
+        <v>3.2868</v>
       </c>
       <c r="V22" t="n">
         <v>-2.8215</v>
